--- a/test_sets/deals/packet_4_atlantic_beverage_proceed/Atlantic_Beverage_3Yr_Audited_Financial_Model.xlsx
+++ b/test_sets/deals/packet_4_atlantic_beverage_proceed/Atlantic_Beverage_3Yr_Audited_Financial_Model.xlsx
@@ -545,7 +545,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Audited 5-Year Financial Track Record | Grant Thornton LLP</t>
+          <t>Audited 5-Year Financial Track Record | Kentmere Ashford LLP</t>
         </is>
       </c>
     </row>
